--- a/Resources/CabinetTemplate.xlsx
+++ b/Resources/CabinetTemplate.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Ace\excel-ct-tools\bin\Debug\net48\publish\Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Ace\excel-ct-tools\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D44C9464-0320-4F31-8B80-F207BC9A130D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6957B36F-FE30-4D41-BD66-8E481910297B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="98">
   <si>
     <t>序号</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -429,16 +429,7 @@
     <t>类别</t>
   </si>
   <si>
-    <t>物料编码</t>
-  </si>
-  <si>
-    <t>产地</t>
-  </si>
-  <si>
     <t>加工费</t>
-  </si>
-  <si>
-    <t>订货号</t>
   </si>
   <si>
     <t>人工</t>
@@ -1779,6 +1770,60 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1796,60 +1841,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2280,23 +2271,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="198" t="str">
+      <c r="A1" s="214" t="str">
         <f>T(B22)</f>
         <v>扬州华科</v>
       </c>
-      <c r="B1" s="198"/>
-      <c r="C1" s="198"/>
-      <c r="D1" s="198"/>
+      <c r="B1" s="214"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="199" t="str">
+      <c r="A2" s="215" t="str">
         <f>T(B23)</f>
         <v/>
       </c>
-      <c r="B2" s="199"/>
-      <c r="C2" s="199"/>
-      <c r="D2" s="199"/>
+      <c r="B2" s="215"/>
+      <c r="C2" s="215"/>
+      <c r="D2" s="215"/>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
@@ -2310,14 +2301,14 @@
       <c r="H3" s="5"/>
     </row>
     <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="200" t="s">
+      <c r="A4" s="216" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="200"/>
-      <c r="C4" s="200"/>
-      <c r="D4" s="200"/>
-      <c r="E4" s="200"/>
-      <c r="F4" s="200"/>
+      <c r="B4" s="216"/>
+      <c r="C4" s="216"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
       <c r="G4" s="4"/>
       <c r="H4" s="5"/>
     </row>
@@ -2325,9 +2316,9 @@
       <c r="A5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="201"/>
-      <c r="C5" s="202"/>
-      <c r="D5" s="203"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="218"/>
+      <c r="D5" s="219"/>
       <c r="E5" s="6" t="s">
         <v>7</v>
       </c>
@@ -2355,9 +2346,9 @@
       <c r="A7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="201"/>
-      <c r="C7" s="202"/>
-      <c r="D7" s="203"/>
+      <c r="B7" s="217"/>
+      <c r="C7" s="218"/>
+      <c r="D7" s="219"/>
       <c r="E7" s="9"/>
       <c r="F7" s="10"/>
       <c r="G7" s="4"/>
@@ -2365,10 +2356,10 @@
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B8" s="183" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C8" s="197"/>
       <c r="D8" s="184"/>
@@ -2426,12 +2417,12 @@
       <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="204" t="s">
+      <c r="A13" s="211" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="205"/>
-      <c r="C13" s="205"/>
-      <c r="D13" s="206"/>
+      <c r="B13" s="212"/>
+      <c r="C13" s="212"/>
+      <c r="D13" s="213"/>
       <c r="E13" s="11"/>
       <c r="F13" s="12"/>
       <c r="G13" s="4"/>
@@ -2522,12 +2513,12 @@
       <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="204" t="s">
+      <c r="A21" s="211" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="205"/>
-      <c r="C21" s="205"/>
-      <c r="D21" s="206"/>
+      <c r="B21" s="212"/>
+      <c r="C21" s="212"/>
+      <c r="D21" s="213"/>
       <c r="E21" s="11"/>
       <c r="F21" s="12"/>
       <c r="G21" s="4"/>
@@ -2538,7 +2529,7 @@
         <v>25</v>
       </c>
       <c r="B22" s="183" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C22" s="197"/>
       <c r="D22" s="184"/>
@@ -2596,12 +2587,12 @@
       <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="207" t="s">
+      <c r="A27" s="198" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="208"/>
-      <c r="C27" s="208"/>
-      <c r="D27" s="209"/>
+      <c r="B27" s="199"/>
+      <c r="C27" s="199"/>
+      <c r="D27" s="200"/>
       <c r="E27" s="13"/>
       <c r="F27" s="14"/>
       <c r="G27" s="4"/>
@@ -3042,33 +3033,33 @@
       <c r="B56" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="C56" s="210" t="str">
+      <c r="C56" s="201" t="str">
         <f ca="1">TEXT(SUBSTITUTE(IF(D55="","",IF(MOD(D55,1)=0,TEXT(INT(D55),"[DBNum2][$-804]G/通用格式元整"),(TEXT(INT(D55),"[DBNum2][$-804]G/通用格式元")&amp;TEXT((INT(D55*10)-INT(D55)*10),"[DBNum2][$-804]G/通用格式角")&amp;TEXT((INT(D55*100)-INT(D55*10)*10),"[DBNum2][$-804]G/通用格式分")))),"零角","零"),)</f>
         <v>零元整</v>
       </c>
-      <c r="D56" s="211"/>
+      <c r="D56" s="202"/>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
       <c r="H56" s="5"/>
     </row>
     <row r="57" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="212" t="s">
+      <c r="A57" s="203" t="s">
         <v>41</v>
       </c>
-      <c r="B57" s="214"/>
-      <c r="C57" s="215"/>
-      <c r="D57" s="216"/>
+      <c r="B57" s="205"/>
+      <c r="C57" s="206"/>
+      <c r="D57" s="207"/>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
       <c r="H57" s="5"/>
     </row>
     <row r="58" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="213"/>
-      <c r="B58" s="217"/>
-      <c r="C58" s="218"/>
-      <c r="D58" s="219"/>
+      <c r="A58" s="204"/>
+      <c r="B58" s="208"/>
+      <c r="C58" s="209"/>
+      <c r="D58" s="210"/>
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
       <c r="G58" s="4"/>
@@ -3083,12 +3074,18 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="B57:D58"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="B14:D14"/>
@@ -3101,18 +3098,12 @@
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="B57:D58"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations disablePrompts="1" count="1">
@@ -3136,7 +3127,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64F42C16-0E02-45B5-8A6E-93E7DC082CF9}">
-  <dimension ref="A1:X75"/>
+  <dimension ref="A1:U75"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -3148,14 +3139,13 @@
     <col min="12" max="12" width="7.5" customWidth="1"/>
     <col min="13" max="13" width="12.625" customWidth="1"/>
     <col min="14" max="14" width="9.75" customWidth="1"/>
-    <col min="15" max="15" width="7.5" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="12.625" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="7.5" customWidth="1"/>
+    <col min="16" max="16" width="12.625" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="19" width="9.75" customWidth="1"/>
-    <col min="20" max="21" width="0" hidden="1" customWidth="1"/>
-    <col min="22" max="23" width="8.75" customWidth="1"/>
+    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="19" max="20" width="8.75" customWidth="1"/>
+    <col min="22" max="22" width="0" hidden="1" customWidth="1"/>
     <col min="25" max="25" width="0" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.15">
@@ -3288,12 +3278,12 @@
         <v>1</v>
       </c>
       <c r="B7" s="67" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C7" s="67"/>
       <c r="D7" s="67"/>
       <c r="E7" s="68" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F7" s="68">
         <v>1</v>
@@ -3890,7 +3880,7 @@
       <c r="P32" s="74"/>
       <c r="Q32" s="90"/>
     </row>
-    <row r="33" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="46">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -3926,7 +3916,7 @@
       <c r="P33" s="74"/>
       <c r="Q33" s="90"/>
     </row>
-    <row r="34" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="46">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -3962,7 +3952,7 @@
       <c r="P34" s="74"/>
       <c r="Q34" s="90"/>
     </row>
-    <row r="35" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="46">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -4007,7 +3997,7 @@
       <c r="P35" s="100"/>
       <c r="Q35" s="101"/>
     </row>
-    <row r="36" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="187" t="s">
         <v>61</v>
       </c>
@@ -4028,7 +4018,7 @@
       <c r="P36" s="4"/>
       <c r="Q36" s="4"/>
     </row>
-    <row r="37" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="188"/>
       <c r="B37" s="193"/>
       <c r="C37" s="193"/>
@@ -4047,7 +4037,7 @@
       <c r="P37" s="4"/>
       <c r="Q37" s="4"/>
     </row>
-    <row r="38" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="103"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -4066,7 +4056,7 @@
       <c r="P38" s="4"/>
       <c r="Q38" s="4"/>
     </row>
-    <row r="39" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="103"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -4085,7 +4075,7 @@
       <c r="P39" s="4"/>
       <c r="Q39" s="4"/>
     </row>
-    <row r="40" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="105" t="str">
         <f>CONCATENATE("报价人：",项目信息!B8)</f>
         <v>报价人：李四</v>
@@ -4110,7 +4100,7 @@
       <c r="P40" s="4"/>
       <c r="Q40" s="4"/>
     </row>
-    <row r="41" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="175" t="str">
         <f>T(项目信息!$B$22)</f>
         <v>扬州华科</v>
@@ -4125,11 +4115,8 @@
       <c r="I41" s="175"/>
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
-      <c r="S41" s="1"/>
-      <c r="T41" s="1"/>
-      <c r="U41" s="1"/>
-    </row>
-    <row r="42" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="42" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="176" t="str">
         <f>T(项目信息!$B$23)</f>
         <v/>
@@ -4144,11 +4131,8 @@
       <c r="I42" s="176"/>
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
-      <c r="S42" s="1"/>
-      <c r="T42" s="1"/>
-      <c r="U42" s="1"/>
-    </row>
-    <row r="43" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="43" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="196" t="s">
         <v>64</v>
       </c>
@@ -4162,16 +4146,13 @@
       <c r="I43" s="196"/>
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
-      <c r="S43" s="1"/>
-      <c r="T43" s="1"/>
-      <c r="U43" s="1"/>
-    </row>
-    <row r="44" spans="1:24" s="128" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="44" spans="1:21" s="128" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="120" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B44" s="121" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C44" s="122" t="s">
         <v>65</v>
@@ -4207,11 +4188,8 @@
       </c>
       <c r="Q44" s="5"/>
       <c r="R44" s="5"/>
-      <c r="S44" s="5"/>
-      <c r="T44" s="5"/>
-      <c r="U44" s="5"/>
-    </row>
-    <row r="45" spans="1:24" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="45" spans="1:21" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="15" t="s">
         <v>29</v>
       </c>
@@ -4272,20 +4250,11 @@
       <c r="T45" s="134" t="s">
         <v>85</v>
       </c>
-      <c r="U45" s="134" t="s">
-        <v>86</v>
-      </c>
-      <c r="V45" s="134" t="s">
-        <v>87</v>
-      </c>
-      <c r="W45" s="134" t="s">
-        <v>88</v>
-      </c>
-      <c r="X45" s="135" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U45" s="135" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="64">
         <f t="shared" ref="A46:A70" si="1">ROW()-ROW(A$45)</f>
         <v>1</v>
@@ -4347,22 +4316,13 @@
       <c r="R46" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S46" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T46" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U46" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V46" s="142"/>
-      <c r="W46" s="142"/>
-      <c r="X46" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S46" s="142"/>
+      <c r="T46" s="142"/>
+      <c r="U46" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="46">
         <f t="shared" si="1"/>
         <v>2</v>
@@ -4424,22 +4384,13 @@
       <c r="R47" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S47" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T47" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U47" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V47" s="142"/>
-      <c r="W47" s="142"/>
-      <c r="X47" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S47" s="142"/>
+      <c r="T47" s="142"/>
+      <c r="U47" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="46">
         <f t="shared" si="1"/>
         <v>3</v>
@@ -4501,22 +4452,13 @@
       <c r="R48" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S48" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T48" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U48" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V48" s="142"/>
-      <c r="W48" s="142"/>
-      <c r="X48" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S48" s="142"/>
+      <c r="T48" s="142"/>
+      <c r="U48" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="46">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -4578,22 +4520,13 @@
       <c r="R49" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S49" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T49" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U49" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V49" s="142"/>
-      <c r="W49" s="142"/>
-      <c r="X49" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S49" s="142"/>
+      <c r="T49" s="142"/>
+      <c r="U49" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="46">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -4655,22 +4588,13 @@
       <c r="R50" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S50" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T50" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U50" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V50" s="142"/>
-      <c r="W50" s="142"/>
-      <c r="X50" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S50" s="142"/>
+      <c r="T50" s="142"/>
+      <c r="U50" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="46">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -4732,22 +4656,13 @@
       <c r="R51" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S51" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T51" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U51" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V51" s="142"/>
-      <c r="W51" s="142"/>
-      <c r="X51" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S51" s="142"/>
+      <c r="T51" s="142"/>
+      <c r="U51" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="46">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -4809,22 +4724,13 @@
       <c r="R52" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S52" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T52" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U52" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V52" s="142"/>
-      <c r="W52" s="142"/>
-      <c r="X52" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S52" s="142"/>
+      <c r="T52" s="142"/>
+      <c r="U52" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="46">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -4886,22 +4792,13 @@
       <c r="R53" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S53" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T53" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U53" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V53" s="142"/>
-      <c r="W53" s="142"/>
-      <c r="X53" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S53" s="142"/>
+      <c r="T53" s="142"/>
+      <c r="U53" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="46">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -4963,22 +4860,13 @@
       <c r="R54" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S54" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T54" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U54" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V54" s="142"/>
-      <c r="W54" s="142"/>
-      <c r="X54" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S54" s="142"/>
+      <c r="T54" s="142"/>
+      <c r="U54" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="46">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -5040,22 +4928,13 @@
       <c r="R55" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S55" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T55" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U55" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V55" s="142"/>
-      <c r="W55" s="142"/>
-      <c r="X55" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S55" s="142"/>
+      <c r="T55" s="142"/>
+      <c r="U55" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="46">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -5117,22 +4996,13 @@
       <c r="R56" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S56" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T56" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U56" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V56" s="142"/>
-      <c r="W56" s="142"/>
-      <c r="X56" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S56" s="142"/>
+      <c r="T56" s="142"/>
+      <c r="U56" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="46">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -5194,22 +5064,13 @@
       <c r="R57" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S57" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T57" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U57" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V57" s="142"/>
-      <c r="W57" s="142"/>
-      <c r="X57" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S57" s="142"/>
+      <c r="T57" s="142"/>
+      <c r="U57" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="46">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -5271,22 +5132,13 @@
       <c r="R58" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S58" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T58" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U58" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V58" s="142"/>
-      <c r="W58" s="142"/>
-      <c r="X58" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S58" s="142"/>
+      <c r="T58" s="142"/>
+      <c r="U58" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="46">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -5348,22 +5200,13 @@
       <c r="R59" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S59" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T59" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U59" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V59" s="142"/>
-      <c r="W59" s="142"/>
-      <c r="X59" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S59" s="142"/>
+      <c r="T59" s="142"/>
+      <c r="U59" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="46">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -5425,22 +5268,13 @@
       <c r="R60" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S60" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T60" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U60" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V60" s="142"/>
-      <c r="W60" s="142"/>
-      <c r="X60" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S60" s="142"/>
+      <c r="T60" s="142"/>
+      <c r="U60" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="46">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -5502,22 +5336,13 @@
       <c r="R61" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S61" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T61" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U61" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V61" s="142"/>
-      <c r="W61" s="142"/>
-      <c r="X61" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="62" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S61" s="142"/>
+      <c r="T61" s="142"/>
+      <c r="U61" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="46">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -5579,22 +5404,13 @@
       <c r="R62" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S62" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T62" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U62" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V62" s="142"/>
-      <c r="W62" s="142"/>
-      <c r="X62" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S62" s="142"/>
+      <c r="T62" s="142"/>
+      <c r="U62" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="46">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -5656,22 +5472,13 @@
       <c r="R63" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S63" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T63" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U63" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V63" s="142"/>
-      <c r="W63" s="142"/>
-      <c r="X63" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="64" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S63" s="142"/>
+      <c r="T63" s="142"/>
+      <c r="U63" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="46">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -5733,22 +5540,13 @@
       <c r="R64" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S64" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T64" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U64" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V64" s="142"/>
-      <c r="W64" s="142"/>
-      <c r="X64" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="65" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S64" s="142"/>
+      <c r="T64" s="142"/>
+      <c r="U64" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="46">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -5810,22 +5608,13 @@
       <c r="R65" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S65" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T65" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U65" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V65" s="142"/>
-      <c r="W65" s="142"/>
-      <c r="X65" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="66" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S65" s="142"/>
+      <c r="T65" s="142"/>
+      <c r="U65" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="46">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -5859,34 +5648,25 @@
       <c r="R66" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S66" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T66" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U66" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V66" s="142">
-        <f>ROUND(SUMPRODUCT(F45:INDEX(F:F,ROW()-1),V45:INDEX(V:V,ROW()-1)),2)</f>
+      <c r="S66" s="142">
+        <f>ROUND(SUMPRODUCT(F45:INDEX(F:F,ROW()-1),S45:INDEX(S:S,ROW()-1)),2)</f>
         <v>0</v>
       </c>
-      <c r="W66" s="142">
-        <f>ROUND(SUMPRODUCT(F45:INDEX(F:F,ROW()-1),W45:INDEX(W:W,ROW()-1)),2)</f>
+      <c r="T66" s="142">
+        <f>ROUND(SUMPRODUCT(F45:INDEX(F:F,ROW()-1),T45:INDEX(T:T,ROW()-1)),2)</f>
         <v>0</v>
       </c>
-      <c r="X66" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U66" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="46">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="B67" s="145" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C67" s="146"/>
       <c r="D67" s="102"/>
@@ -5894,7 +5674,7 @@
       <c r="F67" s="77"/>
       <c r="G67" s="111"/>
       <c r="H67" s="111">
-        <f>ROUND(V66*1.18,0)</f>
+        <f>ROUND(S66*1.18,0)</f>
         <v>0</v>
       </c>
       <c r="I67" s="69" t="s">
@@ -5911,33 +5691,24 @@
       <c r="O67" s="139"/>
       <c r="P67" s="171"/>
       <c r="Q67" s="140" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="R67" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S67" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T67" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U67" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V67" s="142"/>
-      <c r="W67" s="142"/>
-      <c r="X67" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="68" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S67" s="142"/>
+      <c r="T67" s="142"/>
+      <c r="U67" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="46">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="B68" s="145" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C68" s="146"/>
       <c r="D68" s="102"/>
@@ -5962,28 +5733,19 @@
       <c r="R68" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S68" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T68" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U68" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V68" s="142"/>
-      <c r="W68" s="142"/>
-      <c r="X68" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S68" s="142"/>
+      <c r="T68" s="142"/>
+      <c r="U68" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="46">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="B69" s="145" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C69" s="146"/>
       <c r="D69" s="102"/>
@@ -6005,33 +5767,24 @@
       <c r="O69" s="139"/>
       <c r="P69" s="171"/>
       <c r="Q69" s="140" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="R69" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S69" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T69" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U69" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V69" s="142"/>
-      <c r="W69" s="142"/>
-      <c r="X69" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S69" s="142"/>
+      <c r="T69" s="142"/>
+      <c r="U69" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="46">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="B70" s="102" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C70" s="146"/>
       <c r="D70" s="102"/>
@@ -6057,24 +5810,15 @@
       <c r="R70" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S70" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T70" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U70" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V70" s="142"/>
-      <c r="W70" s="142"/>
-      <c r="X70" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="71" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S70" s="142"/>
+      <c r="T70" s="142"/>
+      <c r="U70" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="151" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B71" s="152"/>
       <c r="C71" s="153"/>
@@ -6108,22 +5852,13 @@
       <c r="R71" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="S71" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="T71" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="U71" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="V71" s="142"/>
-      <c r="W71" s="142"/>
-      <c r="X71" s="143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="72" spans="1:24" s="128" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S71" s="142"/>
+      <c r="T71" s="142"/>
+      <c r="U71" s="143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" s="128" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="103"/>
       <c r="B72" s="126" t="s">
         <v>8</v>
@@ -6136,14 +5871,11 @@
       </c>
       <c r="Q72" s="5"/>
       <c r="R72" s="5"/>
-      <c r="S72" s="5"/>
-      <c r="T72" s="5"/>
-      <c r="U72" s="5"/>
-      <c r="X72" s="126" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="1:24" s="128" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U72" s="126" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" s="128" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="103"/>
       <c r="B73" s="126" t="s">
         <v>8</v>
@@ -6156,14 +5888,11 @@
       </c>
       <c r="Q73" s="5"/>
       <c r="R73" s="5"/>
-      <c r="S73" s="5"/>
-      <c r="T73" s="5"/>
-      <c r="U73" s="5"/>
-      <c r="X73" s="126" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U73" s="126" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="173" t="str" cm="1">
         <f t="array" aca="1" ref="A74" ca="1">CONCATENATE("报价人：", INDIRECT("项目信息!$B$8"))</f>
         <v>报价人：李四</v>
@@ -6180,14 +5909,11 @@
       </c>
       <c r="Q74" s="5"/>
       <c r="R74" s="5"/>
-      <c r="S74" s="5"/>
-      <c r="T74" s="5"/>
-      <c r="U74" s="5"/>
-      <c r="X74" s="135" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U74" s="135" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="159"/>
     </row>
   </sheetData>
